--- a/1_01 _comparativaterritorial.xlsx
+++ b/1_01 _comparativaterritorial.xlsx
@@ -1,12 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lquifez.inserta\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F78FFD-8118-41D9-B99E-E198BB812808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Hoja 1" sheetId="1" r:id="rId5"/>
+    <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -82,70 +104,70 @@
     <t>Rioja, La</t>
   </si>
   <si>
-    <t>Ceuta y Melilla</t>
-  </si>
-  <si>
     <t>Melilla</t>
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>Ceuta</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="Roboto"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Roboto"/>
     </font>
     <font>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
     </font>
@@ -155,7 +177,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -177,11 +199,21 @@
     </fill>
   </fills>
   <borders count="6">
-    <border/>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FFC00000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -196,19 +228,27 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FFF2F2F2"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FFC00000"/>
       </top>
       <bottom style="thin">
         <color rgb="FFF2F2F2"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -217,69 +257,67 @@
       <right style="thin">
         <color rgb="FFFFFFFF"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" vertical="top"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="6" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="3" fillId="2" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="5" fillId="4" fontId="6" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -469,21 +507,24 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="36.0"/>
-    <col customWidth="1" min="5" max="5" width="18.75"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -503,467 +544,476 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="5">
-        <v>373100.0</v>
+        <v>373100</v>
       </c>
       <c r="C2" s="6">
-        <f t="shared" ref="C2:C21" si="1">B2/$B$21*100</f>
-        <v>19.21710018</v>
+        <f t="shared" ref="C2:C21" si="0">B2/$B$21*100</f>
+        <v>19.217100180272983</v>
       </c>
       <c r="D2" s="7">
-        <v>382300.0</v>
+        <v>382300</v>
       </c>
       <c r="E2" s="8">
-        <f t="shared" ref="E2:E21" si="2">D2/$D$21*100</f>
-        <v>19.63735361</v>
+        <f t="shared" ref="E2:E21" si="1">D2/$D$21*100</f>
+        <v>19.637353605917404</v>
       </c>
       <c r="F2" s="8">
-        <f t="shared" ref="F2:F21" si="3">(B2-D2)/D2*100</f>
-        <v>-2.406487052</v>
-      </c>
-    </row>
-    <row r="3">
+        <f t="shared" ref="F2:F21" si="2">(B2-D2)/D2*100</f>
+        <v>-2.406487052053361</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="10">
-        <v>39900.0</v>
+        <v>39900</v>
       </c>
       <c r="C3" s="6">
-        <f t="shared" si="1"/>
-        <v>2.055112027</v>
+        <f t="shared" si="0"/>
+        <v>2.0551120267834149</v>
       </c>
       <c r="D3" s="7">
-        <v>41200.0</v>
+        <v>41200</v>
       </c>
       <c r="E3" s="8">
-        <f t="shared" si="2"/>
-        <v>2.116293405</v>
+        <f t="shared" si="1"/>
+        <v>2.1162934045613313</v>
       </c>
       <c r="F3" s="8">
-        <f t="shared" si="3"/>
-        <v>-3.155339806</v>
-      </c>
-    </row>
-    <row r="4">
+        <f t="shared" si="2"/>
+        <v>-3.1553398058252426</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="10">
-        <v>49400.0</v>
+        <v>49400</v>
       </c>
       <c r="C4" s="6">
-        <f t="shared" si="1"/>
-        <v>2.544424414</v>
+        <f t="shared" si="0"/>
+        <v>2.5444244141127994</v>
       </c>
       <c r="D4" s="7">
-        <v>53000.0</v>
+        <v>53000</v>
       </c>
       <c r="E4" s="8">
-        <f t="shared" si="2"/>
-        <v>2.722416273</v>
+        <f t="shared" si="1"/>
+        <v>2.7224162728580232</v>
       </c>
       <c r="F4" s="8">
-        <f t="shared" si="3"/>
-        <v>-6.79245283</v>
-      </c>
-    </row>
-    <row r="5">
+        <f t="shared" si="2"/>
+        <v>-6.7924528301886795</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="10">
-        <v>33900.0</v>
+        <v>33900</v>
       </c>
       <c r="C5" s="6">
-        <f t="shared" si="1"/>
-        <v>1.746072624</v>
+        <f t="shared" si="0"/>
+        <v>1.7460726242595932</v>
       </c>
       <c r="D5" s="7">
-        <v>36100.0</v>
+        <v>36100</v>
       </c>
       <c r="E5" s="8">
-        <f t="shared" si="2"/>
-        <v>1.854325046</v>
+        <f t="shared" si="1"/>
+        <v>1.8543250462297105</v>
       </c>
       <c r="F5" s="8">
-        <f t="shared" si="3"/>
-        <v>-6.094182825</v>
-      </c>
-    </row>
-    <row r="6">
+        <f t="shared" si="2"/>
+        <v>-6.094182825484765</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="10">
-        <v>97500.0</v>
+        <v>97500</v>
       </c>
       <c r="C6" s="6">
-        <f t="shared" si="1"/>
-        <v>5.021890291</v>
+        <f t="shared" si="0"/>
+        <v>5.0218902910121042</v>
       </c>
       <c r="D6" s="7">
-        <v>96800.0</v>
+        <v>96800</v>
       </c>
       <c r="E6" s="8">
-        <f t="shared" si="2"/>
-        <v>4.972262174</v>
+        <f t="shared" si="1"/>
+        <v>4.9722621738237107</v>
       </c>
       <c r="F6" s="8">
-        <f t="shared" si="3"/>
-        <v>0.7231404959</v>
-      </c>
-    </row>
-    <row r="7">
+        <f t="shared" si="2"/>
+        <v>0.72314049586776863</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="10">
-        <v>31600.0</v>
+        <v>31600</v>
       </c>
       <c r="C7" s="6">
-        <f t="shared" si="1"/>
-        <v>1.62760752</v>
+        <f t="shared" si="0"/>
+        <v>1.6276075199587947</v>
       </c>
       <c r="D7" s="7">
-        <v>31000.0</v>
+        <v>31000</v>
       </c>
       <c r="E7" s="8">
-        <f t="shared" si="2"/>
-        <v>1.592356688</v>
+        <f t="shared" si="1"/>
+        <v>1.5923566878980893</v>
       </c>
       <c r="F7" s="8">
-        <f t="shared" si="3"/>
-        <v>1.935483871</v>
-      </c>
-    </row>
-    <row r="8">
+        <f t="shared" si="2"/>
+        <v>1.935483870967742</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="10">
-        <v>94100.0</v>
+        <v>94100</v>
       </c>
       <c r="C8" s="6">
-        <f t="shared" si="1"/>
-        <v>4.846767963</v>
+        <f t="shared" si="0"/>
+        <v>4.8467679629152718</v>
       </c>
       <c r="D8" s="7">
-        <v>94400.0</v>
+        <v>94400</v>
       </c>
       <c r="E8" s="8">
-        <f t="shared" si="2"/>
-        <v>4.848982946</v>
+        <f t="shared" si="1"/>
+        <v>4.8489829463735363</v>
       </c>
       <c r="F8" s="8">
-        <f t="shared" si="3"/>
-        <v>-0.3177966102</v>
-      </c>
-    </row>
-    <row r="9">
+        <f t="shared" si="2"/>
+        <v>-0.31779661016949157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="10">
-        <v>93300.0</v>
+        <v>93300</v>
       </c>
       <c r="C9" s="6">
-        <f t="shared" si="1"/>
-        <v>4.805562709</v>
+        <f t="shared" si="0"/>
+        <v>4.8055627092454287</v>
       </c>
       <c r="D9" s="7">
-        <v>94000.0</v>
+        <v>94000</v>
       </c>
       <c r="E9" s="8">
-        <f t="shared" si="2"/>
-        <v>4.828436408</v>
+        <f t="shared" si="1"/>
+        <v>4.8284364084651736</v>
       </c>
       <c r="F9" s="8">
-        <f t="shared" si="3"/>
-        <v>-0.7446808511</v>
-      </c>
-    </row>
-    <row r="10">
+        <f t="shared" si="2"/>
+        <v>-0.74468085106382986</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="10">
-        <v>343900.0</v>
+        <v>343900</v>
       </c>
       <c r="C10" s="6">
-        <f t="shared" si="1"/>
-        <v>17.71310842</v>
+        <f t="shared" si="0"/>
+        <v>17.713108421323721</v>
       </c>
       <c r="D10" s="7">
-        <v>337200.0</v>
+        <v>337200</v>
       </c>
       <c r="E10" s="8">
-        <f t="shared" si="2"/>
-        <v>17.32073146</v>
+        <f t="shared" si="1"/>
+        <v>17.320731456749538</v>
       </c>
       <c r="F10" s="8">
-        <f t="shared" si="3"/>
-        <v>1.986951364</v>
-      </c>
-    </row>
-    <row r="11">
+        <f t="shared" si="2"/>
+        <v>1.9869513641755634</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B11" s="10">
-        <v>187600.0</v>
+        <v>187600</v>
       </c>
       <c r="C11" s="6">
-        <f t="shared" si="1"/>
-        <v>9.662631986</v>
+        <f t="shared" si="0"/>
+        <v>9.6626319855781606</v>
       </c>
       <c r="D11" s="7">
-        <v>188100.0</v>
+        <v>188100</v>
       </c>
       <c r="E11" s="8">
-        <f t="shared" si="2"/>
-        <v>9.662009451</v>
+        <f t="shared" si="1"/>
+        <v>9.6620094514074388</v>
       </c>
       <c r="F11" s="8">
-        <f t="shared" si="3"/>
-        <v>-0.2658160553</v>
-      </c>
-    </row>
-    <row r="12">
+        <f t="shared" si="2"/>
+        <v>-0.26581605528973951</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="10">
-        <v>46100.0</v>
+        <v>46100</v>
       </c>
       <c r="C12" s="6">
-        <f t="shared" si="1"/>
-        <v>2.374452743</v>
+        <f t="shared" si="0"/>
+        <v>2.3744527427246975</v>
       </c>
       <c r="D12" s="7">
-        <v>46200.0</v>
+        <v>46200</v>
       </c>
       <c r="E12" s="8">
-        <f t="shared" si="2"/>
-        <v>2.373125128</v>
+        <f t="shared" si="1"/>
+        <v>2.3731251284158619</v>
       </c>
       <c r="F12" s="8">
-        <f t="shared" si="3"/>
-        <v>-0.2164502165</v>
-      </c>
-    </row>
-    <row r="13">
+        <f t="shared" si="2"/>
+        <v>-0.21645021645021645</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="10">
-        <v>136600.0</v>
+        <v>136600</v>
       </c>
       <c r="C13" s="6">
-        <f t="shared" si="1"/>
-        <v>7.035797064</v>
+        <f t="shared" si="0"/>
+        <v>7.035797064125676</v>
       </c>
       <c r="D13" s="7">
-        <v>135000.0</v>
+        <v>135000</v>
       </c>
       <c r="E13" s="8">
-        <f t="shared" si="2"/>
-        <v>6.934456544</v>
+        <f t="shared" si="1"/>
+        <v>6.9344565440723231</v>
       </c>
       <c r="F13" s="8">
-        <f t="shared" si="3"/>
-        <v>1.185185185</v>
-      </c>
-    </row>
-    <row r="14">
+        <f t="shared" si="2"/>
+        <v>1.1851851851851851</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>18</v>
       </c>
       <c r="B14" s="10">
-        <v>216300.0</v>
+        <v>216300</v>
       </c>
       <c r="C14" s="6">
-        <f t="shared" si="1"/>
-        <v>11.14087046</v>
+        <f t="shared" si="0"/>
+        <v>11.140870460983777</v>
       </c>
       <c r="D14" s="7">
-        <v>213700.0</v>
+        <v>213700</v>
       </c>
       <c r="E14" s="8">
-        <f t="shared" si="2"/>
-        <v>10.97698788</v>
+        <f t="shared" si="1"/>
+        <v>10.976987877542633</v>
       </c>
       <c r="F14" s="8">
-        <f t="shared" si="3"/>
-        <v>1.216658868</v>
-      </c>
-    </row>
-    <row r="15">
+        <f t="shared" si="2"/>
+        <v>1.2166588675713619</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="10">
-        <v>78600.0</v>
+        <v>78600</v>
       </c>
       <c r="C15" s="6">
-        <f t="shared" si="1"/>
-        <v>4.048416173</v>
+        <f t="shared" si="0"/>
+        <v>4.0484161730620656</v>
       </c>
       <c r="D15" s="7">
-        <v>78500.0</v>
+        <v>78500</v>
       </c>
       <c r="E15" s="8">
-        <f t="shared" si="2"/>
-        <v>4.032258065</v>
+        <f t="shared" si="1"/>
+        <v>4.032258064516129</v>
       </c>
       <c r="F15" s="8">
-        <f t="shared" si="3"/>
-        <v>0.127388535</v>
-      </c>
-    </row>
-    <row r="16">
+        <f t="shared" si="2"/>
+        <v>0.12738853503184713</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>20</v>
       </c>
       <c r="B16" s="10">
-        <v>21500.0</v>
+        <v>21500</v>
       </c>
       <c r="C16" s="6">
-        <f t="shared" si="1"/>
-        <v>1.107391192</v>
+        <f t="shared" si="0"/>
+        <v>1.1073911923770281</v>
       </c>
       <c r="D16" s="7">
-        <v>20700.0</v>
+        <v>20700</v>
       </c>
       <c r="E16" s="8">
-        <f t="shared" si="2"/>
-        <v>1.063283337</v>
+        <f t="shared" si="1"/>
+        <v>1.0632833367577563</v>
       </c>
       <c r="F16" s="8">
-        <f t="shared" si="3"/>
-        <v>3.8647343</v>
-      </c>
-    </row>
-    <row r="17">
+        <f t="shared" si="2"/>
+        <v>3.8647342995169081</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="10">
-        <v>77200.0</v>
+        <v>77200</v>
       </c>
       <c r="C17" s="6">
-        <f t="shared" si="1"/>
-        <v>3.976306979</v>
+        <f t="shared" si="0"/>
+        <v>3.9763069791398404</v>
       </c>
       <c r="D17" s="7">
-        <v>77700.0</v>
+        <v>77700</v>
       </c>
       <c r="E17" s="8">
-        <f t="shared" si="2"/>
-        <v>3.991164989</v>
+        <f t="shared" si="1"/>
+        <v>3.9911649886994041</v>
       </c>
       <c r="F17" s="8">
-        <f t="shared" si="3"/>
-        <v>-0.6435006435</v>
-      </c>
-    </row>
-    <row r="18">
+        <f t="shared" si="2"/>
+        <v>-0.64350064350064351</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="10">
-        <v>10200.0</v>
+        <v>10200</v>
       </c>
       <c r="C18" s="6">
-        <f t="shared" si="1"/>
-        <v>0.5253669843</v>
+        <f t="shared" si="0"/>
+        <v>0.52536698429049711</v>
       </c>
       <c r="D18" s="7">
-        <v>10100.0</v>
+        <v>10100</v>
       </c>
       <c r="E18" s="8">
-        <f t="shared" si="2"/>
-        <v>0.5188000822</v>
+        <f t="shared" si="1"/>
+        <v>0.51880008218615159</v>
       </c>
       <c r="F18" s="8">
-        <f t="shared" si="3"/>
-        <v>0.9900990099</v>
-      </c>
-    </row>
-    <row r="19">
+        <f t="shared" si="2"/>
+        <v>0.99009900990099009</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="10">
+        <v>10700</v>
+      </c>
+      <c r="C19" s="6">
+        <f t="shared" si="0"/>
+        <v>0.55112026783414891</v>
+      </c>
+      <c r="D19" s="7">
+        <v>10800</v>
+      </c>
+      <c r="E19" s="8">
+        <f t="shared" si="1"/>
+        <v>0.55475652352578586</v>
+      </c>
+      <c r="F19" s="8">
+        <f t="shared" si="2"/>
+        <v>-0.92592592592592582</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="10">
-        <v>10700.0</v>
-      </c>
-      <c r="C19" s="6">
-        <f t="shared" si="1"/>
-        <v>0.5511202678</v>
-      </c>
-      <c r="D19" s="7">
-        <v>10800.0</v>
-      </c>
-      <c r="E19" s="8">
-        <f t="shared" si="2"/>
-        <v>0.5547565235</v>
-      </c>
-      <c r="F19" s="8">
-        <f t="shared" si="3"/>
-        <v>-0.9259259259</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="s">
+      <c r="B20" s="10">
+        <v>10700</v>
+      </c>
+      <c r="C20" s="6">
+        <f t="shared" si="0"/>
+        <v>0.55112026783414891</v>
+      </c>
+      <c r="D20" s="7">
+        <v>10800</v>
+      </c>
+      <c r="E20" s="8">
+        <f t="shared" si="1"/>
+        <v>0.55475652352578586</v>
+      </c>
+      <c r="F20" s="8">
+        <f t="shared" si="2"/>
+        <v>-0.92592592592592582</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="10">
-        <v>10700.0</v>
-      </c>
-      <c r="C20" s="6">
-        <f t="shared" si="1"/>
-        <v>0.5511202678</v>
-      </c>
-      <c r="D20" s="7">
-        <v>10800.0</v>
-      </c>
-      <c r="E20" s="8">
-        <f t="shared" si="2"/>
-        <v>0.5547565235</v>
-      </c>
-      <c r="F20" s="8">
-        <f t="shared" si="3"/>
-        <v>-0.9259259259</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="s">
-        <v>25</v>
-      </c>
       <c r="B21" s="10">
-        <v>1941500.0</v>
+        <v>1941500</v>
       </c>
       <c r="C21" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="D21" s="12">
-        <v>1946800.0</v>
+        <v>1946800</v>
       </c>
       <c r="E21" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="F21" s="8">
-        <f t="shared" si="3"/>
-        <v>-0.2722416273</v>
+        <f t="shared" si="2"/>
+        <v>-0.27224162728580237</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Clasificación: Interna</oddFooter>
+  </headerFooter>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{d958723a-5915-4af3-b4cd-4da9a9655e8a}" enabled="1" method="Standard" siteId="{bab5b22c-d82b-452e-9cad-04f9708f4bbd}" contentBits="2" removed="0"/>
+</clbl:labelList>
 </file>